--- a/13158_Cuenca_Sama/_raw_reportes_xlsx/IDConfig_67641_completo.xlsx
+++ b/13158_Cuenca_Sama/_raw_reportes_xlsx/IDConfig_67641_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R0d5237b19a814bac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R8221d399eb854b34"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5140</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4677</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4375</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4677</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4525</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4677</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4375</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4525</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4375</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/13158_Cuenca_Sama/_raw_reportes_xlsx/IDConfig_67641_completo.xlsx
+++ b/13158_Cuenca_Sama/_raw_reportes_xlsx/IDConfig_67641_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R8221d399eb854b34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rca83fe4bf0ad4356"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9779</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1490</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9594</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8862</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3502</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3502</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4226</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3932</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3932</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3644</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3644</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3644</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3644</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3502</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3224</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3362</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3502</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3087</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3362</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3362</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3362</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3087</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3224</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3362</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3224</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3087</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3087</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2817</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3224</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3224</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3224</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3644</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3932</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3932</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3932</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4226</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4375</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,28 +984,913 @@
         </x:is>
       </x:c>
       <x:c s="3">
+        <x:v>      0.4226</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3932</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3644</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3932</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3932</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3644</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3644</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3644</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3644</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3502</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3362</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3644</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3845</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3644</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3644</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3644</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3502</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3644</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3644</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3644</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4375</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3932</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4226</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3932</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4375</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4226</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4226</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3932</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4226</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4226</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4375</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
         <x:v>      0.5140</x:v>
       </x:c>
     </x:row>
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>22/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4677</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/08/2026</x:t>
+          <x:t>29/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4525</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3932</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3644</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -300,52 +1905,112 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>20/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4677</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4525</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4677</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/08/2026</x:t>
+          <x:t>22/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3932</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4226</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3932</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -360,82 +2025,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>16/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4525</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4375</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4375</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4375</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4226</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/08/2026</x:t>
+          <x:t>14/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -450,247 +2040,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>10/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4226</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3787</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3787</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3845</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3787</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3644</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3644</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3644</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3502</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3787</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>31/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3787</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3644</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3787</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3787</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3644</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3644</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/07/2026</x:t>
+          <x:t>13/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -705,7 +2055,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>24/07/2026</x:t>
+          <x:t>12/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -720,37 +2070,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>23/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4375</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3932</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/07/2026</x:t>
+          <x:t>11/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -765,606 +2085,6 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>20/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4226</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4078</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4078</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3932</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4375</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4226</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4226</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4078</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4078</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3787</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4078</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3932</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4078</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4078</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4078</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4078</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4078</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4226</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4226</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4375</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.5140</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4525</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3932</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3644</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3787</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4078</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4078</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4375</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3932</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4078</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4226</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4078</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4078</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3932</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3787</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4375</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4078</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4078</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4078</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4078</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
           <x:t>10/06/2026</x:t>
         </x:is>
       </x:c>
@@ -1374,7 +2094,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5937</x:v>
+        <x:v>      0.4830</x:v>
       </x:c>
     </x:row>
     <x:row>
